--- a/aralik/ozdilekteyim-aralik-2026-arama-talebi.xlsx
+++ b/aralik/ozdilekteyim-aralik-2026-arama-talebi.xlsx
@@ -3893,17 +3893,23 @@
         <v>0</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="J63" s="10" t="n">
-        <v>0.09090909090909091</v>
-      </c>
-      <c r="K63" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J63" s="5" t="n">
         <v>-0.2</v>
       </c>
-      <c r="L63" s="4" t="inlineStr"/>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>bere modelleri</t>
+        </is>
+      </c>
       <c r="M63" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
@@ -22797,141 +22803,145 @@
           <t>bere</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr"/>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>bere modelleri</t>
+        </is>
+      </c>
       <c r="C63" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H63" s="3" t="n">
         <v>24</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M63" s="3" t="n">
         <v>31</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O63" s="3" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="P63" s="3" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="R63" s="3" t="n">
         <v>100</v>
       </c>
       <c r="S63" s="3" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="T63" s="3" t="n">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="U63" s="3" t="n">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="V63" s="3" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="W63" s="3" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="X63" s="3" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Y63" s="3" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Z63" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA63" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB63" s="3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AC63" s="3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AD63" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE63" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="AE63" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="AF63" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG63" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AH63" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AI63" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ63" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL63" s="3" t="n">
         <v>9</v>
       </c>
       <c r="AM63" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN63" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO63" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP63" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AN63" s="3" t="n">
+      <c r="AQ63" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR63" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="AO63" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AP63" s="3" t="n">
+      <c r="AS63" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="AQ63" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR63" s="3" t="n">
+      <c r="AT63" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU63" s="3" t="n">
         <v>10</v>
-      </c>
-      <c r="AS63" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT63" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU63" s="3" t="n">
-        <v>12</v>
       </c>
       <c r="AV63" s="3" t="n">
         <v>11</v>
@@ -22943,19 +22953,19 @@
         <v>10</v>
       </c>
       <c r="AY63" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ63" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA63" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BB63" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="BC63" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">

--- a/aralik/ozdilekteyim-aralik-2026-arama-talebi.xlsx
+++ b/aralik/ozdilekteyim-aralik-2026-arama-talebi.xlsx
@@ -12328,267 +12328,267 @@
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>21 Eyl 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>21-27 Eylül 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>28 Eyl 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>28 Eylül - 4 Ekim 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>5 Eki 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>5-11 Ekim 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
-          <t>12 Eki 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>12-18 Ekim 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="G1" s="8" t="inlineStr">
         <is>
-          <t>19 Eki 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>19-25 Ekim 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="H1" s="8" t="inlineStr">
         <is>
-          <t>26 Eki 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>26 Ekim - 1 Kasım 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="I1" s="8" t="inlineStr">
         <is>
-          <t>2 Kas 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>2-8 Kasım 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="J1" s="8" t="inlineStr">
         <is>
-          <t>9 Kas 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>9-15 Kasım 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="K1" s="8" t="inlineStr">
         <is>
-          <t>16 Kas 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>16-22 Kasım 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="L1" s="8" t="inlineStr">
         <is>
-          <t>23 Kas 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>23-29 Kasım 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="M1" s="8" t="inlineStr">
         <is>
-          <t>30 Kas 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>30 Kasım - 6 Aralık 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="N1" s="8" t="inlineStr">
         <is>
-          <t>7 Ara 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>7-13 Aralık 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="O1" s="8" t="inlineStr">
         <is>
-          <t>14 Ara 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>14-20 Aralık 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="P1" s="8" t="inlineStr">
         <is>
-          <t>21 Ara 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>21-27 Aralık 2025 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="Q1" s="8" t="inlineStr">
         <is>
-          <t>28 Ara 2025 haftası · Trends 0-100 (Google Trends)</t>
+          <t>28 Aralık 2025 - 3 Ocak 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="R1" s="8" t="inlineStr">
         <is>
-          <t>4 Oca 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>4-10 Ocak 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="S1" s="8" t="inlineStr">
         <is>
-          <t>11 Oca 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>11-17 Ocak 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="T1" s="8" t="inlineStr">
         <is>
-          <t>18 Oca 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>18-24 Ocak 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="U1" s="8" t="inlineStr">
         <is>
-          <t>25 Oca 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>25-31 Ocak 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="V1" s="8" t="inlineStr">
         <is>
-          <t>1 Şub 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>1-7 Şubat 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="W1" s="8" t="inlineStr">
         <is>
-          <t>8 Şub 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>8-14 Şubat 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="X1" s="8" t="inlineStr">
         <is>
-          <t>15 Şub 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>15-21 Şubat 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="Y1" s="8" t="inlineStr">
         <is>
-          <t>22 Şub 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>22-28 Şubat 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="Z1" s="8" t="inlineStr">
         <is>
-          <t>1 Mar 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>1-7 Mart 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AA1" s="8" t="inlineStr">
         <is>
-          <t>8 Mar 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>8-14 Mart 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AB1" s="8" t="inlineStr">
         <is>
-          <t>15 Mar 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>15-21 Mart 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AC1" s="8" t="inlineStr">
         <is>
-          <t>22 Mar 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>22-28 Mart 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AD1" s="8" t="inlineStr">
         <is>
-          <t>29 Mar 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>29 Mart - 4 Nisan 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AE1" s="8" t="inlineStr">
         <is>
-          <t>5 Nis 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>5-11 Nisan 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AF1" s="8" t="inlineStr">
         <is>
-          <t>12 Nis 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>12-18 Nisan 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AG1" s="8" t="inlineStr">
         <is>
-          <t>19 Nis 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>19-25 Nisan 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AH1" s="8" t="inlineStr">
         <is>
-          <t>26 Nis 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>26 Nisan - 2 Mayıs 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AI1" s="8" t="inlineStr">
         <is>
-          <t>3 May 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>3-9 Mayıs 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AJ1" s="8" t="inlineStr">
         <is>
-          <t>10 May 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>10-16 Mayıs 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AK1" s="8" t="inlineStr">
         <is>
-          <t>17 May 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>17-23 Mayıs 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AL1" s="8" t="inlineStr">
         <is>
-          <t>24 May 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>24-30 Mayıs 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AM1" s="8" t="inlineStr">
         <is>
-          <t>31 May 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>31 Mayıs - 6 Haziran 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AN1" s="8" t="inlineStr">
         <is>
-          <t>7 Haz 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>7-13 Haziran 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AO1" s="8" t="inlineStr">
         <is>
-          <t>14 Haz 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>14-20 Haziran 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AP1" s="8" t="inlineStr">
         <is>
-          <t>21 Haz 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>21-27 Haziran 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AQ1" s="8" t="inlineStr">
         <is>
-          <t>28 Haz 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>28 Haziran - 4 Temmuz 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AR1" s="8" t="inlineStr">
         <is>
-          <t>5 Tem 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>5-11 Temmuz 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AS1" s="8" t="inlineStr">
         <is>
-          <t>12 Tem 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>12-18 Temmuz 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AT1" s="8" t="inlineStr">
         <is>
-          <t>19 Tem 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>19-25 Temmuz 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AU1" s="8" t="inlineStr">
         <is>
-          <t>26 Tem 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>26 Temmuz - 1 Ağustos 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AV1" s="8" t="inlineStr">
         <is>
-          <t>2 Ağu 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>2-8 Ağustos 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AW1" s="8" t="inlineStr">
         <is>
-          <t>9 Ağu 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>9-15 Ağustos 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AX1" s="8" t="inlineStr">
         <is>
-          <t>16 Ağu 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>16-22 Ağustos 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AY1" s="8" t="inlineStr">
         <is>
-          <t>23 Ağu 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>23-29 Ağustos 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="AZ1" s="8" t="inlineStr">
         <is>
-          <t>30 Ağu 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>30 Ağustos - 5 Eylül 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="BA1" s="8" t="inlineStr">
         <is>
-          <t>6 Eyl 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>6-12 Eylül 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="BB1" s="8" t="inlineStr">
         <is>
-          <t>13 Eyl 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>13-19 Eylül 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
       <c r="BC1" s="8" t="inlineStr">
         <is>
-          <t>20 Eyl 2026 haftası · Trends 0-100 (Google Trends)</t>
+          <t>20-26 Eylül 2026 · Trends 0-100 (Google Trends)</t>
         </is>
       </c>
     </row>
